--- a/artfynd/A 64150-2023 artfynd.xlsx
+++ b/artfynd/A 64150-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64150-2023 artfynd.xlsx
+++ b/artfynd/A 64150-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94941294</v>
+        <v>94941216</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Attsjö 342, Sm</t>
+          <t>Attsjö 348, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506986.0039363924</v>
+        <v>506843</v>
       </c>
       <c r="R2" t="n">
-        <v>6305321.014411902</v>
+        <v>6305155</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2016-06-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-10-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +789,7 @@
         <v>94941253</v>
       </c>
       <c r="B3" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506924.380329619</v>
+        <v>506925</v>
       </c>
       <c r="R3" t="n">
-        <v>6305188.183717328</v>
+        <v>6305188</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,19 +854,9 @@
           <t>2016-06-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-10-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94941216</v>
+        <v>94941294</v>
       </c>
       <c r="B4" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,14 +928,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Attsjö 348, Sm</t>
+          <t>Attsjö 342, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506843.981272486</v>
+        <v>506986</v>
       </c>
       <c r="R4" t="n">
-        <v>6305154.1855182</v>
+        <v>6305320</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,19 +965,9 @@
           <t>2016-06-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-10-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 64150-2023 artfynd.xlsx
+++ b/artfynd/A 64150-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Inventering av tall- och granproduktionsskog i södra Småland</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94941216</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Inventering av tall- och granproduktionsskog i södra Småland</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94941253</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,8 +1020,18 @@
           <t>Inventering av tall- och granproduktionsskog i södra Småland</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94941294</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>